--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrPlanAssetR002.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrPlanAssetR002.xlsx
@@ -3,6 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IdeaProjects\GUANGZHOU\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="12915" windowHeight="5985"/>
   </bookViews>
@@ -10,7 +15,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -20,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>组合代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -83,6 +87,10 @@
   </si>
   <si>
     <t>投资经理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前处理人</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -519,6 +527,9 @@
       <c r="P1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="2" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.15">
       <c r="K2" s="4"/>
